--- a/test-reports/Board_Test_Report.xlsx
+++ b/test-reports/Board_Test_Report.xlsx
@@ -549,7 +549,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>#18</t>
+          <t>#19</t>
         </is>
       </c>
       <c r="C2" s="4" t="n"/>
@@ -564,7 +564,7 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>Tuesday 30 June 2026 12:04:39 PM IST</t>
+          <t>Tuesday 30 June 2026 12:18:52 PM IST</t>
         </is>
       </c>
       <c r="C3" s="7" t="n"/>

--- a/test-reports/Board_Test_Report.xlsx
+++ b/test-reports/Board_Test_Report.xlsx
@@ -549,7 +549,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>#19</t>
+          <t>#21</t>
         </is>
       </c>
       <c r="C2" s="4" t="n"/>
@@ -564,7 +564,7 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>Tuesday 30 June 2026 12:18:52 PM IST</t>
+          <t>Tuesday 30 June 2026 12:31:51 PM IST</t>
         </is>
       </c>
       <c r="C3" s="7" t="n"/>

--- a/test-reports/Board_Test_Report.xlsx
+++ b/test-reports/Board_Test_Report.xlsx
@@ -549,7 +549,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>#21</t>
+          <t>#22</t>
         </is>
       </c>
       <c r="C2" s="4" t="n"/>
@@ -564,7 +564,7 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>Tuesday 30 June 2026 12:31:51 PM IST</t>
+          <t>Tuesday 30 June 2026 12:42:14 PM IST</t>
         </is>
       </c>
       <c r="C3" s="7" t="n"/>

--- a/test-reports/Board_Test_Report.xlsx
+++ b/test-reports/Board_Test_Report.xlsx
@@ -549,7 +549,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>#22</t>
+          <t>#23</t>
         </is>
       </c>
       <c r="C2" s="4" t="n"/>
@@ -564,7 +564,7 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>Tuesday 30 June 2026 12:42:14 PM IST</t>
+          <t>Tuesday 30 June 2026 12:44:58 PM IST</t>
         </is>
       </c>
       <c r="C3" s="7" t="n"/>

--- a/test-reports/Board_Test_Report.xlsx
+++ b/test-reports/Board_Test_Report.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,43 +26,19 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="16"/>
+      <color rgb="FFFFFFFF"/>
     </font>
     <font>
-      <name val="Arial"/>
       <b val="1"/>
-      <sz val="11"/>
+      <color rgb="FF000000"/>
     </font>
     <font>
-      <name val="Arial"/>
-      <sz val="11"/>
+      <color rgb="FF000000"/>
     </font>
     <font>
-      <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="001E7B34"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="001E7B34"/>
-      <sz val="13"/>
+      <color rgb="FF1E7B34"/>
     </font>
   </fonts>
   <fills count="7">
@@ -74,27 +50,32 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E79"/>
+        <fgColor rgb="FF1F4E79"/>
+        <bgColor rgb="FF1F4E79"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002E75B6"/>
+        <fgColor rgb="FF2E75B6"/>
+        <bgColor rgb="FF2E75B6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor rgb="FFC6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -108,55 +89,38 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFCCCCCC"/>
       </left>
       <right style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFCCCCCC"/>
       </right>
       <top style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFCCCCCC"/>
       </top>
       <bottom style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFCCCCCC"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -522,26 +486,26 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="58.32" customWidth="1" min="1" max="1"/>
+    <col width="51.04" customWidth="1" min="2" max="2"/>
+    <col width="50.71" customWidth="1" min="3" max="3"/>
+    <col width="25.91" customWidth="1" min="4" max="4"/>
+    <col width="60.42" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
+    <row r="1" ht="27.75" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>JENKINS BOARD TEST REPORT</t>
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="15" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Build Number</t>
@@ -549,29 +513,23 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>#23</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="n"/>
-      <c r="D2" s="4" t="n"/>
-      <c r="E2" s="4" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+          <t>#26</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>Build Time</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
-        <is>
-          <t>Tuesday 30 June 2026 12:44:58 PM IST</t>
-        </is>
-      </c>
-      <c r="C3" s="7" t="n"/>
-      <c r="D3" s="7" t="n"/>
-      <c r="E3" s="7" t="n"/>
-    </row>
-    <row r="4">
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Tuesday 30 June 2026 03:38:02 PM IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Board IP</t>
@@ -582,26 +540,20 @@
           <t>192.168.11.173</t>
         </is>
       </c>
-      <c r="C4" s="4" t="n"/>
-      <c r="D4" s="4" t="n"/>
-      <c r="E4" s="4" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Board User</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>root</t>
         </is>
       </c>
-      <c r="C5" s="7" t="n"/>
-      <c r="D5" s="7" t="n"/>
-      <c r="E5" s="7" t="n"/>
-    </row>
-    <row r="6">
+    </row>
+    <row r="6" ht="15" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Agent Used</t>
@@ -612,73 +564,151 @@
           <t>local-ssh-agent</t>
         </is>
       </c>
-      <c r="C6" s="4" t="n"/>
-      <c r="D6" s="4" t="n"/>
-      <c r="E6" s="4" t="n"/>
-    </row>
-    <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
+    </row>
+    <row r="8" ht="21.75" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>TEST RESULTS</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A9" s="1" t="inlineStr">
         <is>
           <t>1. Board Reachable</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="1" t="inlineStr">
         <is>
           <t>2. SSH Connection</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C9" s="1" t="inlineStr">
         <is>
           <t>3. GPIO Discovery</t>
         </is>
       </c>
-      <c r="D9" s="9" t="inlineStr">
+      <c r="D9" s="1" t="inlineStr">
         <is>
           <t>4. Pin Test</t>
         </is>
       </c>
-      <c r="E9" s="9" t="inlineStr">
+      <c r="E9" s="1" t="inlineStr">
         <is>
           <t>5. Functional Test</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+    <row r="10" ht="345.5" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>+ ping -c 3 192.168.11.173
+PING 192.168.11.173 (192.168.11.173) 56(84) bytes of data.
+64 bytes from 192.168.11.173: icmp_seq=1 ttl=64 time=0.451 ms
+64 bytes from 192.168.11.173: icmp_seq=2 ttl=64 time=0.341 ms
+64 bytes from 192.168.11.173: icmp_seq=3 ttl=64 time=0.414 ms
+--- 192.168.11.173 ping statistics ---
+3 packets transmitted, 3 received, 0% packet loss, time 2081ms
+rtt min/avg/max/mdev = 0.341/0.402/0.451/0.045 ms
++ echo ✅ Board is REACHABLE!
+✅ Board is REACHABLE!</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>+ ssh -o StrictHostKeyChecking=no root@192.168.11.173 echo ✅ SSH Connected! &amp;&amp; hostname &amp;&amp; uptime
+✅ SSH Connected!
+rugged-board-a5d2x-sd1
+ 04:05:48 up  4:03,  load average: 0.00, 0.00, 0.00</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>+ ssh -o StrictHostKeyChecking=no root@192.168.11.173 echo "--- /sys/class/gpio ---"
+                                        ls /sys/class/gpio 2&gt;/dev/null || echo "not present"
+                                        echo "--- gpiochip devices ---"
+                                        ls /dev/gpiochip* 2&gt;/dev/null || echo "not present"
+                                        echo "--- libgpiod tools ---"
+                                        which gpioget gpioset 2&gt;/dev/null || echo "libgpiod not installed"
+                                        echo "--- Board Info ---"
+                                        cat /proc/cpuinfo | grep "model name" | head -n 1
+                                        uname -a
+--- /sys/class/gpio ---
+PA1
+PC21
+export
+gpiochip0
+unexport
+--- gpiochip devices ---
+/dev/gpiochip0
+--- libgpiod tools ---
+libgpiod not installed
+--- Board Info ---
+model name	: ARMv7 Processor rev 1 (v7l)
+Linux rugged-board-a5d2x-sd1 4.9.151-linux4sam_5.8+-04826-gef5e9ce04d43-dirty #1 Fri Aug 19 14:54:55 IST 2022 armv7l GNU/Linux</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>+ ssh -o StrictHostKeyChecking=no root@192.168.11.173 echo "=== GPIO Pin Test ==="
+                                        echo 1 &gt; /sys/class/gpio/export 2&gt;/dev/null || true
+                                        sleep 1
+                                        ls /sys/class/gpio/ 2&gt;/dev/null
+                                        echo "Pin test completed!"
+=== GPIO Pin Test ===
+PA1
+PC21
+export
+gpiochip0
+unexport
+Pin test completed!</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>+ ssh -o StrictHostKeyChecking=no root@192.168.11.173 /bin/sh
+=== System Functional Test ===
+CPU:
+model name	: ARMv7 Processor rev 1 (v7l)
+Memory:
+Mem:         55000      14816      40184          4       1704       4896
+Disk:
+/dev/root                 7.1G    187.8M      6.6G   3% /
+Uptime:
+ 04:05:53 up  4:03,  load average: 0.00, 0.00, 0.00
+✅ Functional test PASSED!</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="13.8" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>PASSED ✅</t>
         </is>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>PASSED ✅</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>PASSED ✅</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr">
+      <c r="D11" s="8" t="inlineStr">
         <is>
           <t>PASSED ✅</t>
         </is>
       </c>
-      <c r="E10" s="10" t="inlineStr">
+      <c r="E11" s="8" t="inlineStr">
         <is>
           <t>PASSED ✅</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="26" customHeight="1">
-      <c r="A12" s="11" t="inlineStr">
+    <row r="13" ht="25.5" customHeight="1">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>STATUS: ALL TESTS PASSED ✅</t>
         </is>
@@ -686,7 +716,6 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A12:E12"/>
     <mergeCell ref="B4:E4"/>
     <mergeCell ref="B6:E6"/>
     <mergeCell ref="A8:E8"/>
@@ -694,8 +723,8 @@
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="B5:E5"/>
     <mergeCell ref="B2:E2"/>
+    <mergeCell ref="A13:E13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/test-reports/Board_Test_Report.xlsx
+++ b/test-reports/Board_Test_Report.xlsx
@@ -38,7 +38,7 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="FF1E7B34"/>
+      <color rgb="FF9C0006"/>
     </font>
   </fonts>
   <fills count="7">
@@ -74,8 +74,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor rgb="FFFFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -513,7 +513,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>#26</t>
+          <t>#29</t>
         </is>
       </c>
     </row>
@@ -525,7 +525,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>Tuesday 30 June 2026 03:38:02 PM IST</t>
+          <t>Tuesday 30 June 2026 04:38:31 PM IST</t>
         </is>
       </c>
     </row>
@@ -604,113 +604,63 @@
         <is>
           <t>+ ping -c 3 192.168.11.173
 PING 192.168.11.173 (192.168.11.173) 56(84) bytes of data.
-64 bytes from 192.168.11.173: icmp_seq=1 ttl=64 time=0.451 ms
-64 bytes from 192.168.11.173: icmp_seq=2 ttl=64 time=0.341 ms
-64 bytes from 192.168.11.173: icmp_seq=3 ttl=64 time=0.414 ms
 --- 192.168.11.173 ping statistics ---
-3 packets transmitted, 3 received, 0% packet loss, time 2081ms
-rtt min/avg/max/mdev = 0.341/0.402/0.451/0.045 ms
-+ echo ✅ Board is REACHABLE!
-✅ Board is REACHABLE!</t>
+3 packets transmitted, 0 received, 100% packet loss, time 2079ms</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
           <t>+ ssh -o StrictHostKeyChecking=no root@192.168.11.173 echo ✅ SSH Connected! &amp;&amp; hostname &amp;&amp; uptime
-✅ SSH Connected!
-rugged-board-a5d2x-sd1
- 04:05:48 up  4:03,  load average: 0.00, 0.00, 0.00</t>
+Terminated</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>+ ssh -o StrictHostKeyChecking=no root@192.168.11.173 echo "--- /sys/class/gpio ---"
-                                        ls /sys/class/gpio 2&gt;/dev/null || echo "not present"
-                                        echo "--- gpiochip devices ---"
-                                        ls /dev/gpiochip* 2&gt;/dev/null || echo "not present"
-                                        echo "--- libgpiod tools ---"
-                                        which gpioget gpioset 2&gt;/dev/null || echo "libgpiod not installed"
-                                        echo "--- Board Info ---"
-                                        cat /proc/cpuinfo | grep "model name" | head -n 1
-                                        uname -a
---- /sys/class/gpio ---
-PA1
-PC21
-export
-gpiochip0
-unexport
---- gpiochip devices ---
-/dev/gpiochip0
---- libgpiod tools ---
-libgpiod not installed
---- Board Info ---
-model name	: ARMv7 Processor rev 1 (v7l)
-Linux rugged-board-a5d2x-sd1 4.9.151-linux4sam_5.8+-04826-gef5e9ce04d43-dirty #1 Fri Aug 19 14:54:55 IST 2022 armv7l GNU/Linux</t>
+          <t>(no output captured)</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>+ ssh -o StrictHostKeyChecking=no root@192.168.11.173 echo "=== GPIO Pin Test ==="
-                                        echo 1 &gt; /sys/class/gpio/export 2&gt;/dev/null || true
-                                        sleep 1
-                                        ls /sys/class/gpio/ 2&gt;/dev/null
-                                        echo "Pin test completed!"
-=== GPIO Pin Test ===
-PA1
-PC21
-export
-gpiochip0
-unexport
-Pin test completed!</t>
+          <t>(no output captured)</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>+ ssh -o StrictHostKeyChecking=no root@192.168.11.173 /bin/sh
-=== System Functional Test ===
-CPU:
-model name	: ARMv7 Processor rev 1 (v7l)
-Memory:
-Mem:         55000      14816      40184          4       1704       4896
-Disk:
-/dev/root                 7.1G    187.8M      6.6G   3% /
-Uptime:
- 04:05:53 up  4:03,  load average: 0.00, 0.00, 0.00
-✅ Functional test PASSED!</t>
+          <t>(no output captured)</t>
         </is>
       </c>
     </row>
     <row r="11" ht="13.8" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>PASSED ✅</t>
+          <t>FAILED ❌</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>PASSED ✅</t>
+          <t>FAILED ❌</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>PASSED ✅</t>
+          <t>FAILED ❌</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>PASSED ✅</t>
+          <t>FAILED ❌</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>PASSED ✅</t>
+          <t>FAILED ❌</t>
         </is>
       </c>
     </row>
     <row r="13" ht="25.5" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>STATUS: ALL TESTS PASSED ✅</t>
+          <t>STATUS: ONE OR MORE TESTS FAILED ❌</t>
         </is>
       </c>
     </row>

--- a/test-reports/Board_Test_Report.xlsx
+++ b/test-reports/Board_Test_Report.xlsx
@@ -513,7 +513,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>#29</t>
+          <t>#3</t>
         </is>
       </c>
     </row>
@@ -525,7 +525,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>Tuesday 30 June 2026 04:38:31 PM IST</t>
+          <t>Wednesday 01 July 2026 10:58:46 AM IST</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>local-ssh-agent</t>
+          <t>ssh-agent-key</t>
         </is>
       </c>
     </row>
@@ -602,16 +602,17 @@
     <row r="10" ht="345.5" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>+ ping -c 3 192.168.11.173
+          <t>+ echo === Ping Test ===
+=== Ping Test ===
++ ping -c 3 192.168.11.173
 PING 192.168.11.173 (192.168.11.173) 56(84) bytes of data.
 --- 192.168.11.173 ping statistics ---
-3 packets transmitted, 0 received, 100% packet loss, time 2079ms</t>
+3 packets transmitted, 0 received, 100% packet loss, time 2052ms</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>+ ssh -o StrictHostKeyChecking=no root@192.168.11.173 echo ✅ SSH Connected! &amp;&amp; hostname &amp;&amp; uptime
-Terminated</t>
+          <t>(no output captured)</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
